--- a/data/trans_orig/IP19C06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19C06-Clase-trans_orig.xlsx
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67385</t>
+          <t>67344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>122049</t>
+          <t>121664</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32904</t>
+          <t>32926</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72585</t>
+          <t>72661</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5038</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>336650</t>
+          <t>337618</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>660718</t>
+          <t>660533</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45048</t>
+          <t>45252</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50354</t>
+          <t>49520</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97216</t>
+          <t>96624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37655</t>
+          <t>37223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77490</t>
+          <t>77187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87279</t>
+          <t>87733</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>185603</t>
+          <t>185711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68211</t>
+          <t>68040</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150162</t>
+          <t>150261</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>22299</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58537</t>
+          <t>58812</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10233</t>
+          <t>11168</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>329661</t>
+          <t>329129</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>335596</t>
+          <t>335473</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>336563</t>
+          <t>337121</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>342277</t>
+          <t>342280</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>669271</t>
+          <t>668336</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>676877</t>
+          <t>676856</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65251</t>
+          <t>65264</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138111</t>
+          <t>138474</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29419</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>61356</t>
+          <t>62255</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>337769</t>
+          <t>338267</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>686407</t>
+          <t>686888</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64111</t>
+          <t>64290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70562</t>
+          <t>70613</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160852</t>
+          <t>160317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166740</t>
+          <t>166711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59369</t>
+          <t>57934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67167</t>
+          <t>65983</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128119</t>
+          <t>128430</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107526</t>
+          <t>107495</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>234603</t>
+          <t>234276</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65019</t>
+          <t>65641</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>168979</t>
+          <t>168676</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>37463</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>82270</t>
+          <t>82503</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10540</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4188</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>376273</t>
+          <t>376231</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>383853</t>
+          <t>384044</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>470355</t>
+          <t>470627</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>850183</t>
+          <t>851258</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>861117</t>
+          <t>861290</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C06-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP19C06-Clase-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49358</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>54795</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>49358</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49358</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>49358</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49358</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>54795</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>54795</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>54795</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>49358</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>49358</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>49358</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1179,47 +1179,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37046</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>40498</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>37046</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>37046</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37046</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>37046</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>40498</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>40498</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>40498</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>37046</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>37046</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>37046</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53369</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>35010</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>53369</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53369</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>53369</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>53369</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>35010</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>35010</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>35010</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>53369</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>53369</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>53369</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1865,47 +1865,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>96154</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>98137</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>96154</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>96154</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>96154</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>96154</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>98137</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>98137</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>98137</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>96154</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>96154</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>96154</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,107 +2095,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>525</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2691</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2961</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3029</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>69510</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>66673</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>70035</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>54658</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>69510</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>67344</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>70035</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>121664</t>
+          <t>121732</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>70035</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>70035</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>70035</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>54658</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>54658</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>54658</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>70035</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>70035</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>70035</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2438,107 +2438,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2801</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3471</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3066</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2551,72 +2551,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>35032</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>32718</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>35727</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,06%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>91,58%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>35032</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>32926</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>35727</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,06%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72661</t>
+          <t>72256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2664,57 +2664,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>35727</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>35727</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>35727</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>40000</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>40000</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>35727</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>35727</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>35727</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2781,107 +2781,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>1219</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4070</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4026</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4253</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -2894,72 +2894,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>340469</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>337322</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>341688</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>480</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>323098</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>340469</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>337618</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>341688</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>660533</t>
+          <t>660760</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3007,57 +3007,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>341688</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>341688</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>341688</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>480</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>323098</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>323098</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>323098</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>341688</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>341688</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>341688</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3190,7 +3190,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3471,47 +3471,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40884</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>48238</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>40884</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3584,57 +3584,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>40884</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40884</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>40884</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>48238</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>48238</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>48238</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>40884</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>40884</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>40884</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3706,102 +3706,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>430</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3554</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3915</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,7%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3945</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -3814,74 +3814,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>52450</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49930</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>53074</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>47065</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>45252</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>45311</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>47495</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>52450</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>49520</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>53074</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>93,3%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>143</t>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96624</t>
+          <t>96654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3927,57 +3927,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>53074</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>53074</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>53074</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>47495</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>47495</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>47495</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>53074</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>53074</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>53074</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4044,107 +4044,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1283</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4502</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4335</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,07%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4309</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4330</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -4162,69 +4162,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>39791</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>40442</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>37223</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>37390</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>41725</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,93%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>89,61%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>39791</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>118</t>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77187</t>
+          <t>77208</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4270,57 +4270,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39791</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39791</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39791</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>41725</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>41725</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>41725</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39791</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>39791</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4387,107 +4387,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>698</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3495</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3509</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3501</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3484</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4500,74 +4500,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>97966</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>90530</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>87733</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>87719</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>91228</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,23%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>97966</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>270</t>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>185711</t>
+          <t>185694</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4613,57 +4613,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>97966</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>97966</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>97966</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>91228</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>91228</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>91228</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>97966</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>97966</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>97966</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4730,107 +4730,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1599</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5627</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5442</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5634</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -4843,72 +4843,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>72068</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>68763</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>73667</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,34%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>82228</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>72068</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>68040</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>73667</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150261</t>
+          <t>150453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4956,57 +4956,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73667</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>73667</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>73667</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>82228</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>82228</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>82228</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>73667</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>73667</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>73667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5073,107 +5073,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3391</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3993</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>15,54%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4251</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4395</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -5186,74 +5186,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>37516</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>24872</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>22299</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>21697</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>25690</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>96,81%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>86,8%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>84,46%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>37516</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>88</t>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58812</t>
+          <t>58956</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5299,57 +5299,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>37516</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>37516</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>37516</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>25690</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>25690</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>25690</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>37516</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>37516</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>37516</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6040</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>3230</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>1132</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>7476</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>8261</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2223</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5778</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5529,74 +5529,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>340676</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>336859</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>342278</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>475</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>333375</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>329129</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>328344</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>335473</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,04%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>340676</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>337121</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>342280</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>965</t>
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>668336</t>
+          <t>669651</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>676856</t>
+          <t>677307</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -5642,57 +5642,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>342899</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>342899</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>342899</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>480</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>336605</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>336605</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>336605</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>342899</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>342899</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>342899</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5825,7 +5825,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6106,47 +6106,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50514</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>43019</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>50514</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6219,57 +6219,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50514</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50514</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50514</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>43019</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>43019</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>43019</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>50514</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>50514</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>50514</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6449,47 +6449,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54030</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>55734</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>54030</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6562,57 +6562,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>54030</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>54030</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>54030</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>55734</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>55734</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>55734</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>54030</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>54030</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>54030</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6792,47 +6792,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34298</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>31125</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>34298</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6905,57 +6905,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>34298</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34298</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>34298</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>31125</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>31125</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>31125</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>34298</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>34298</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>34298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7135,47 +7135,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>103865</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>111100</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>103865</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7248,57 +7248,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>103865</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>103865</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>103865</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>111100</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>111100</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>111100</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>103865</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>103865</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>103865</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7365,107 +7365,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>771</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3899</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4274</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -7478,74 +7478,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>73585</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>68392</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>65264</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>64494</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>69163</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,89%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,36%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>93,25%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>73585</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>202</t>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138474</t>
+          <t>138873</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7591,57 +7591,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73585</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>73585</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>73585</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>69163</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>69163</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>69163</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>73585</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>73585</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>73585</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7708,107 +7708,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3367</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3208</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3128</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2535</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -7821,74 +7821,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>31984</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>29234</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>29393</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>32601</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>98,11%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>89,67%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>90,16%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>32189</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>89</t>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>62255</t>
+          <t>61662</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7934,57 +7934,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>32189</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>32601</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>32601</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>32601</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>32189</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>32189</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>32189</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8051,107 +8051,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1388</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4476</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4750</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4985</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4336</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -8164,74 +8164,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>348481</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>495</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>341355</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>338267</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>337993</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>342743</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,59%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>348481</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>979</t>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>686888</t>
+          <t>686239</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8277,57 +8277,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>348481</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>348481</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>348481</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>497</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>342743</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>342743</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>342743</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>348481</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>348481</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>348481</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8460,7 +8460,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8628,72 +8628,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1161</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7484</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7842</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -8741,72 +8741,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>90572</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>68472</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>64290</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>70613</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>96090</t>
+          <t>68161</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63668</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70103</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>164562</t>
+          <t>158734</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160317</t>
+          <t>154259</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>166711</t>
+          <t>160996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -8854,57 +8854,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>90572</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>90572</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>90572</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71774</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71774</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71774</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>96090</t>
+          <t>71510</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>96090</t>
+          <t>71510</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>96090</t>
+          <t>71510</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>167864</t>
+          <t>162083</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>167864</t>
+          <t>162083</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>167864</t>
+          <t>162083</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>964</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>821</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -9056,12 +9056,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -9084,74 +9084,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>69443</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>64670</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>70407</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>61893</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>57934</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>62701</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>64417</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>61208</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>65238</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>93,82%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>70543</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>65983</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>71588</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>180</t>
@@ -9159,27 +9159,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>132436</t>
+          <t>133860</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128430</t>
+          <t>130143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134289</t>
+          <t>135645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -9197,57 +9197,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>70407</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>70407</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>70407</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>62701</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>62701</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>62701</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>71588</t>
+          <t>65238</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71588</t>
+          <t>65238</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71588</t>
+          <t>65238</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>134289</t>
+          <t>135645</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>134289</t>
+          <t>135645</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>134289</t>
+          <t>135645</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9427,64 +9427,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34490</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>27928</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>29011</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>36260</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>64188</t>
+          <t>63502</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -9540,57 +9540,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>34490</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>34490</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>34490</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>27928</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>27928</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27928</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>64188</t>
+          <t>63502</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>64188</t>
+          <t>63502</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>64188</t>
+          <t>63502</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9657,107 +9657,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1108</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3552</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4083</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1108</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4163</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -9770,74 +9770,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>109939</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>107495</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>111047</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>107982</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>104940</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>109023</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>127393</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>304</t>
@@ -9845,27 +9845,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>237331</t>
+          <t>230325</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>234276</t>
+          <t>227572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>238439</t>
+          <t>231366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9883,57 +9883,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>122343</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>111047</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>111047</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>111047</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>127393</t>
+          <t>109023</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>127393</t>
+          <t>109023</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>127393</t>
+          <t>109023</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>238439</t>
+          <t>231366</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>238439</t>
+          <t>231366</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>238439</t>
+          <t>231366</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10000,107 +10000,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2857</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2811</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3022</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -10113,74 +10113,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>94025</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>67958</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>65641</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>68498</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>68592</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>66486</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>69070</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>96,26%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>103200</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>200</t>
@@ -10188,27 +10188,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>171158</t>
+          <t>162617</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>168676</t>
+          <t>160284</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>171698</t>
+          <t>163095</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -10226,57 +10226,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>94025</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>94025</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>94025</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>68498</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>68498</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>68498</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>103200</t>
+          <t>69070</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>103200</t>
+          <t>69070</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103200</t>
+          <t>69070</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>171698</t>
+          <t>163095</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>171698</t>
+          <t>163095</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>171698</t>
+          <t>163095</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10343,107 +10343,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6671</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4502</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>15,12%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>6496</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -10456,72 +10456,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>43121</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>40530</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>43762</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>92,61%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>44865</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>47321</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>42802</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>37463</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>44134</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,27 +10531,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>87667</t>
+          <t>90442</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>82503</t>
+          <t>86581</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88999</t>
+          <t>91083</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10569,57 +10569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>43762</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>43762</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>43762</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44865</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44865</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44865</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44134</t>
+          <t>47321</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44134</t>
+          <t>47321</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44134</t>
+          <t>47321</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>88999</t>
+          <t>91083</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>88999</t>
+          <t>91083</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>88999</t>
+          <t>91083</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10686,72 +10686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4845</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5758</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2769</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>10582</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14220</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -10799,72 +10799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>453995</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>450755</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>455600</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>381055</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>376231</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>384044</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>98,51%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>476288</t>
+          <t>385485</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>470627</t>
+          <t>380368</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>478665</t>
+          <t>388472</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>857343</t>
+          <t>839480</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>851258</t>
+          <t>833663</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>861290</t>
+          <t>842940</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -10912,57 +10912,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>455600</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>455600</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>455600</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>547</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>386813</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>386813</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>386813</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>478665</t>
+          <t>391174</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>478665</t>
+          <t>391174</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>478665</t>
+          <t>391174</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>865478</t>
+          <t>846774</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>865478</t>
+          <t>846774</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>865478</t>
+          <t>846774</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
